--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0003T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0003T0006Z000C1N35_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.24029458837236</v>
+        <v>6.376547870610509</v>
       </c>
       <c r="D2" t="n">
-        <v>29.25740476237567</v>
+        <v>4.754328273886046</v>
       </c>
       <c r="E2" t="n">
-        <v>4.383380380814921</v>
+        <v>0.7122993118824246</v>
       </c>
       <c r="F2" t="n">
-        <v>25.23133567960647</v>
+        <v>4.100092047936051</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.41354668369946</v>
+        <v>6.567201336101162</v>
       </c>
       <c r="D3" t="n">
-        <v>49.75718820208571</v>
+        <v>8.085543082838928</v>
       </c>
       <c r="E3" t="n">
-        <v>4.383380380814921</v>
+        <v>0.7122993118824246</v>
       </c>
       <c r="F3" t="n">
-        <v>25.23133567960647</v>
+        <v>4.100092047936051</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.58404685816156</v>
+        <v>4.969907614451254</v>
       </c>
       <c r="D4" t="n">
-        <v>90.00096450100472</v>
+        <v>14.62515673141327</v>
       </c>
       <c r="E4" t="n">
-        <v>4.383380380814921</v>
+        <v>0.7122993118824246</v>
       </c>
       <c r="F4" t="n">
-        <v>25.23133567960647</v>
+        <v>4.100092047936051</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
